--- a/artfynd/A 16161-2026 artfynd.xlsx
+++ b/artfynd/A 16161-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74858879</v>
+        <v>487543</v>
       </c>
       <c r="B2" t="n">
-        <v>100874</v>
+        <v>101345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rugstorp 350m OSO skolan, Sm</t>
+          <t>Rugstorp, 350 m OSO om skolan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570541</v>
+        <v>570491</v>
       </c>
       <c r="R2" t="n">
-        <v>6310700</v>
+        <v>6310729</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -738,6 +738,11 @@
           <t>Bäckebo</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Hf-Nyb-1091</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>1992-01-01</t>
@@ -746,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>1992-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5G2e 2015. SOM: Pulsatilla vernalis. LEG: Inger Bergqvist. KOM: 10-tal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,15 +770,126 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Inger Bergqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74858876</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101344</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rugstorp 350m OSO skolan, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>570541</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6310700</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2002-04-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2002-04-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5G2e 2015. SOM: Pulsatilla vernalis. LEG: Bo Fagerström. KOM: 2/6</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tallås</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 16161-2026 artfynd.xlsx
+++ b/artfynd/A 16161-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/487543</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74858876</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>